--- a/電腦密碼pass.xlsx
+++ b/電腦密碼pass.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1080131\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE45A3D-C0EA-49C9-8C31-DEDC0233DE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C20FA74-E1A6-4CA9-B27B-0BC22507D8F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3072" yWindow="720" windowWidth="25656" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -31,20 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="79">
   <si>
     <t>債券等殖</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>John副總</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a234567</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>人資網</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -89,10 +81,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>snow810820</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1080131@taishinbank.com.tw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -181,10 +169,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>taishin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1080131@taishinbank.com.tw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -249,10 +233,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IR914</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主管：IR002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -261,18 +241,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Snow810820mark101@</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Snow810820!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Snow810820$</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Aaron的路透(跟Pete共用的)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -288,24 +256,96 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>snow810820!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pete的彭博</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pwu681024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Billy1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IR102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aaron</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aaron168</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>snow810820@</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Snow810820mark101#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BNP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IR630</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Snow810820)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Snow810820mark101&amp;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彭博電腦開機密碼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無(直接按Enter)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Snow810820&amp;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龍潭主管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IR009</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skysky258258</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taishin234567</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IR901</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>帳: IR007
-密: Ird123456789</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Snow810820%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>snow810820!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Taishin789</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Snow810820mark101#</t>
+密: Ird567890123</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aa123456</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -367,7 +407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -384,10 +424,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -729,346 +778,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="工作表1"/>
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="8" max="8" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="H1" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2" s="4">
         <v>1080131</v>
       </c>
       <c r="J2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D3" t="s">
+      <c r="I4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>962847</v>
-      </c>
-      <c r="F3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="H6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="48.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>46010</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2">
-        <v>3</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H9" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="I9" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O9" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="I10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H13" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O9" t="s">
-        <v>44</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="J17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H10" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H11" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="J19" s="4">
         <v>6613</v>
       </c>
     </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:11" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" t="s">
+        <v>74</v>
+      </c>
       <c r="H21" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J21" s="4">
+      <c r="I21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="H22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J22" s="4">
         <v>6613</v>
       </c>
     </row>
-    <row r="24" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="H24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>33</v>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="H25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="H26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" display="Snow810820mark101@" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="I1" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="I17" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="I6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="J3" r:id="rId5" display="snow810820@" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="I20" r:id="rId6" xr:uid="{D1ED0142-6E2B-44B7-8A41-4A53357CDBDB}"/>
-    <hyperlink ref="J5" r:id="rId7" display="Snow810820@" xr:uid="{6688E5B8-7C59-4797-A535-6C589A278E74}"/>
-    <hyperlink ref="J17" r:id="rId8" display="Snow810820@" xr:uid="{BE88183D-829A-490F-AC0A-3084AB8E9484}"/>
-    <hyperlink ref="J6" r:id="rId9" xr:uid="{B6F99AF9-1534-4928-834B-4EDF8210987E}"/>
-    <hyperlink ref="C7" r:id="rId10" display="Snow810820mark101@" xr:uid="{1A92844D-5DE0-4FFF-88C5-077CE7888FF3}"/>
+    <hyperlink ref="J3" r:id="rId1" xr:uid="{16EC53D4-7E9D-4700-9543-E4BB5CBD6B50}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>